--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.42324956554818</v>
+        <v>53.31282452178361</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.55530259078361</v>
+        <v>80.77839032504596</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.10383765354738</v>
+        <v>45.77137754170364</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.978395561288568</v>
+        <v>1.956455939607926</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.644003005789318e-24</v>
+        <v>1.619339098466204e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>378.799</v>
+        <v>310.3194031417837</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>927.8773333333334</v>
+        <v>838.4737019144443</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1537.737333333333</v>
+        <v>1467.244488186022</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237.006</v>
+        <v>231.07899636618</v>
       </c>
     </row>
     <row r="6">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.79000000000001</v>
+        <v>98.79335175026156</v>
       </c>
     </row>
     <row r="8">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2667.959</v>
+        <v>2433.659274692026</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.55530259078361</v>
+        <v>80.77839032504596</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.55530259078361</v>
+        <v>80.77839032504596</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>51.80391217980402</v>
+        <v>46.32478633800815</v>
       </c>
       <c r="F11" t="n">
-        <v>40.9624435789366</v>
+        <v>36.62998346709286</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>50.10383765354738</v>
+        <v>45.77137754170364</v>
       </c>
     </row>
     <row r="13">
@@ -1107,7 +1107,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.63762869921814</v>
+        <v>37.54928866420648</v>
       </c>
       <c r="C2" t="n">
-        <v>49.89068903807375</v>
+        <v>45.29130649868561</v>
       </c>
       <c r="D2" t="n">
-        <v>58.14374937692936</v>
+        <v>53.03332433316479</v>
       </c>
       <c r="E2" t="n">
-        <v>66.39680971578497</v>
+        <v>60.77534216764396</v>
       </c>
       <c r="F2" t="n">
-        <v>74.64987005464057</v>
+        <v>68.51736000212308</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.77737879352755</v>
+        <v>37.68903875851589</v>
       </c>
       <c r="C3" t="n">
-        <v>50.03043913238316</v>
+        <v>45.43105659299502</v>
       </c>
       <c r="D3" t="n">
-        <v>58.28349947123877</v>
+        <v>53.17307442747421</v>
       </c>
       <c r="E3" t="n">
-        <v>66.53655981009439</v>
+        <v>60.91509226195336</v>
       </c>
       <c r="F3" t="n">
-        <v>74.78962014894998</v>
+        <v>68.65711009643249</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.91712888783696</v>
+        <v>37.8287888528253</v>
       </c>
       <c r="C4" t="n">
-        <v>50.17018922669257</v>
+        <v>45.57080668730443</v>
       </c>
       <c r="D4" t="n">
-        <v>58.42324956554818</v>
+        <v>53.31282452178361</v>
       </c>
       <c r="E4" t="n">
-        <v>66.67630990440379</v>
+        <v>61.05484235626278</v>
       </c>
       <c r="F4" t="n">
-        <v>74.9293702432594</v>
+        <v>68.79686019074191</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.05687898214637</v>
+        <v>37.96853894713472</v>
       </c>
       <c r="C5" t="n">
-        <v>50.30993932100198</v>
+        <v>45.71055678161384</v>
       </c>
       <c r="D5" t="n">
-        <v>58.5629996598576</v>
+        <v>53.45257461609302</v>
       </c>
       <c r="E5" t="n">
-        <v>66.8160599987132</v>
+        <v>61.19459245057219</v>
       </c>
       <c r="F5" t="n">
-        <v>75.0691203375688</v>
+        <v>68.93661028505132</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.19662907645579</v>
+        <v>38.10828904144413</v>
       </c>
       <c r="C6" t="n">
-        <v>50.44968941531139</v>
+        <v>45.85030687592325</v>
       </c>
       <c r="D6" t="n">
-        <v>58.702749754167</v>
+        <v>53.59232471040244</v>
       </c>
       <c r="E6" t="n">
-        <v>66.95581009302262</v>
+        <v>61.3343425448816</v>
       </c>
       <c r="F6" t="n">
-        <v>75.20887043187821</v>
+        <v>69.07636037936074</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>64.65000000000001</v>
+        <v>59.54</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>66.19</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>66.7</v>
+        <v>61.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.31282452178361</v>
+        <v>53.31536875734308</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.77839032504596</v>
+        <v>80.78724222234649</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45.77137754170364</v>
+        <v>45.76540022797767</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.956455939607926</v>
+        <v>1.956474193423047</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.619339098466204e-24</v>
+        <v>1.619343243217908e-24</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>838.4737019144443</v>
+        <v>838.7403883621116</v>
       </c>
     </row>
     <row r="4">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2433.659274692026</v>
+        <v>2433.925961139693</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80.77839032504596</v>
+        <v>80.78724222234649</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80.77839032504596</v>
+        <v>80.78724222234649</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.32478633800815</v>
+        <v>46.31722701760934</v>
       </c>
       <c r="F11" t="n">
-        <v>36.62998346709286</v>
+        <v>36.62400615336689</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45.77137754170364</v>
+        <v>45.76540022797767</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.54928866420648</v>
+        <v>37.55132405265406</v>
       </c>
       <c r="C2" t="n">
-        <v>45.29130649868561</v>
+        <v>45.29359631068913</v>
       </c>
       <c r="D2" t="n">
-        <v>53.03332433316479</v>
+        <v>53.03586856872425</v>
       </c>
       <c r="E2" t="n">
-        <v>60.77534216764396</v>
+        <v>60.77814082675938</v>
       </c>
       <c r="F2" t="n">
-        <v>68.51736000212308</v>
+        <v>68.52041308479444</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.68903875851589</v>
+        <v>37.69107414696347</v>
       </c>
       <c r="C3" t="n">
-        <v>45.43105659299502</v>
+        <v>45.43334640499854</v>
       </c>
       <c r="D3" t="n">
-        <v>53.17307442747421</v>
+        <v>53.17561866303367</v>
       </c>
       <c r="E3" t="n">
-        <v>60.91509226195336</v>
+        <v>60.91789092106879</v>
       </c>
       <c r="F3" t="n">
-        <v>68.65711009643249</v>
+        <v>68.66016317910385</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.8287888528253</v>
+        <v>37.83082424127289</v>
       </c>
       <c r="C4" t="n">
-        <v>45.57080668730443</v>
+        <v>45.57309649930795</v>
       </c>
       <c r="D4" t="n">
-        <v>53.31282452178361</v>
+        <v>53.31536875734308</v>
       </c>
       <c r="E4" t="n">
-        <v>61.05484235626278</v>
+        <v>61.05764101537819</v>
       </c>
       <c r="F4" t="n">
-        <v>68.79686019074191</v>
+        <v>68.79991327341327</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.96853894713472</v>
+        <v>37.9705743355823</v>
       </c>
       <c r="C5" t="n">
-        <v>45.71055678161384</v>
+        <v>45.71284659361736</v>
       </c>
       <c r="D5" t="n">
-        <v>53.45257461609302</v>
+        <v>53.45511885165249</v>
       </c>
       <c r="E5" t="n">
-        <v>61.19459245057219</v>
+        <v>61.19739110968762</v>
       </c>
       <c r="F5" t="n">
-        <v>68.93661028505132</v>
+        <v>68.93966336772267</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.10828904144413</v>
+        <v>38.11032442989171</v>
       </c>
       <c r="C6" t="n">
-        <v>45.85030687592325</v>
+        <v>45.85259668792678</v>
       </c>
       <c r="D6" t="n">
-        <v>53.59232471040244</v>
+        <v>53.59486894596191</v>
       </c>
       <c r="E6" t="n">
-        <v>61.3343425448816</v>
+        <v>61.33714120399702</v>
       </c>
       <c r="F6" t="n">
-        <v>69.07636037936074</v>
+        <v>69.07941346203209</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>59.54</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>37.14</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.619343243217908e-24</v>
+        <v>1.619343243217907e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.14</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.619343243217907e-24</v>
+        <v>1.619343243217908e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.31536875734308</v>
+        <v>58.08710048881471</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80.78724222234649</v>
+        <v>88.13338101872037</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45.76540022797767</v>
+        <v>49.67247929880576</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.956474193423047</v>
+        <v>1.970759617697794</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.619343243217908e-24</v>
+        <v>1.622586923303446e-24</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>838.7403883621116</v>
+        <v>1060.061941602162</v>
       </c>
     </row>
     <row r="4">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2433.925961139693</v>
+        <v>2655.247514379743</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80.78724222234649</v>
+        <v>88.13338101872037</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80.78724222234649</v>
+        <v>88.13338101872037</v>
       </c>
     </row>
     <row r="20">
@@ -883,13 +883,13 @@
         <v>36628.77482352941</v>
       </c>
       <c r="D2" t="n">
-        <v>4.880244487640473</v>
+        <v>5.04151191264936</v>
       </c>
       <c r="E2" t="n">
-        <v>1.30224645265169</v>
+        <v>1.332887263403379</v>
       </c>
       <c r="F2" t="n">
-        <v>1.268710220217867</v>
+        <v>1.298561950416303</v>
       </c>
     </row>
     <row r="3">
@@ -905,13 +905,13 @@
         <v>38994.77482352941</v>
       </c>
       <c r="D3" t="n">
-        <v>5.34049782823979</v>
+        <v>5.501661365959667</v>
       </c>
       <c r="E3" t="n">
-        <v>1.38969458736556</v>
+        <v>1.420315659532337</v>
       </c>
       <c r="F3" t="n">
-        <v>1.319039729251991</v>
+        <v>1.348103964737602</v>
       </c>
     </row>
     <row r="4">
@@ -927,13 +927,13 @@
         <v>37902.77482352941</v>
       </c>
       <c r="D4" t="n">
-        <v>5.144518909837286</v>
+        <v>5.305724002472768</v>
       </c>
       <c r="E4" t="n">
-        <v>1.352458592869084</v>
+        <v>1.383087560469826</v>
       </c>
       <c r="F4" t="n">
-        <v>1.250638354453765</v>
+        <v>1.278961411322773</v>
       </c>
     </row>
     <row r="5">
@@ -949,13 +949,13 @@
         <v>34626.77482352941</v>
       </c>
       <c r="D5" t="n">
-        <v>4.517974669825893</v>
+        <v>4.679325204665986</v>
       </c>
       <c r="E5" t="n">
-        <v>1.23341518726692</v>
+        <v>1.264071788886537</v>
       </c>
       <c r="F5" t="n">
-        <v>1.111184853393621</v>
+        <v>1.138803413411295</v>
       </c>
     </row>
     <row r="6">
@@ -971,13 +971,13 @@
         <v>33716.77482352941</v>
       </c>
       <c r="D6" t="n">
-        <v>4.348712593948167</v>
+        <v>4.510107651912121</v>
       </c>
       <c r="E6" t="n">
-        <v>1.201255392850152</v>
+        <v>1.231920453863303</v>
       </c>
       <c r="F6" t="n">
-        <v>1.054342290826022</v>
+        <v>1.081257025918461</v>
       </c>
     </row>
     <row r="7">
@@ -993,13 +993,13 @@
         <v>35718.77482352941</v>
       </c>
       <c r="D7" t="n">
-        <v>4.7466246565175</v>
+        <v>4.907912858984188</v>
       </c>
       <c r="E7" t="n">
-        <v>1.276858684738325</v>
+        <v>1.307503443206996</v>
       </c>
       <c r="F7" t="n">
-        <v>1.091838405464325</v>
+        <v>1.118042655489949</v>
       </c>
     </row>
     <row r="8">
@@ -1015,13 +1015,13 @@
         <v>36446.77482352941</v>
       </c>
       <c r="D8" t="n">
-        <v>4.880238551223958</v>
+        <v>5.041505976232845</v>
       </c>
       <c r="E8" t="n">
-        <v>1.302245324732552</v>
+        <v>1.332886135484241</v>
       </c>
       <c r="F8" t="n">
-        <v>1.08486973586422</v>
+        <v>1.110395869562321</v>
       </c>
     </row>
     <row r="9">
@@ -1037,13 +1037,13 @@
         <v>33170.77482352941</v>
       </c>
       <c r="D9" t="n">
-        <v>4.256659551261698</v>
+        <v>4.418075386683454</v>
       </c>
       <c r="E9" t="n">
-        <v>1.183765314739722</v>
+        <v>1.214434323469856</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9607704851389678</v>
+        <v>0.9856621406297021</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.141394074610778</v>
+        <v>9.359788431488404</v>
       </c>
     </row>
     <row r="11">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.31722701760934</v>
+        <v>50.98219039100378</v>
       </c>
       <c r="F11" t="n">
-        <v>36.62400615336689</v>
+        <v>40.31269086731736</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>45.76540022797767</v>
+        <v>49.67247929880576</v>
       </c>
     </row>
     <row r="13">
@@ -1107,7 +1107,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.55132405265406</v>
+        <v>41.38186917125462</v>
       </c>
       <c r="C2" t="n">
-        <v>45.29359631068913</v>
+        <v>49.59476277173053</v>
       </c>
       <c r="D2" t="n">
-        <v>53.03586856872425</v>
+        <v>57.80765637220647</v>
       </c>
       <c r="E2" t="n">
-        <v>60.77814082675938</v>
+        <v>66.02054997268243</v>
       </c>
       <c r="F2" t="n">
-        <v>68.52041308479444</v>
+        <v>74.23344357315834</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.69107414696347</v>
+        <v>41.52159122955874</v>
       </c>
       <c r="C3" t="n">
-        <v>45.43334640499854</v>
+        <v>49.73448483003465</v>
       </c>
       <c r="D3" t="n">
-        <v>53.17561866303367</v>
+        <v>57.94737843051058</v>
       </c>
       <c r="E3" t="n">
-        <v>60.91789092106879</v>
+        <v>66.16027203098655</v>
       </c>
       <c r="F3" t="n">
-        <v>68.66016317910385</v>
+        <v>74.37316563146246</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.83082424127289</v>
+        <v>41.66131328786287</v>
       </c>
       <c r="C4" t="n">
-        <v>45.57309649930795</v>
+        <v>49.87420688833877</v>
       </c>
       <c r="D4" t="n">
-        <v>53.31536875734308</v>
+        <v>58.08710048881471</v>
       </c>
       <c r="E4" t="n">
-        <v>61.05764101537819</v>
+        <v>66.29999408929066</v>
       </c>
       <c r="F4" t="n">
-        <v>68.79991327341327</v>
+        <v>74.51288768976659</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.9705743355823</v>
+        <v>41.80103534616698</v>
       </c>
       <c r="C5" t="n">
-        <v>45.71284659361736</v>
+        <v>50.01392894664289</v>
       </c>
       <c r="D5" t="n">
-        <v>53.45511885165249</v>
+        <v>58.22682254711883</v>
       </c>
       <c r="E5" t="n">
-        <v>61.19739110968762</v>
+        <v>66.43971614759479</v>
       </c>
       <c r="F5" t="n">
-        <v>68.93966336772267</v>
+        <v>74.6526097480707</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.11032442989171</v>
+        <v>41.94075740447111</v>
       </c>
       <c r="C6" t="n">
-        <v>45.85259668792678</v>
+        <v>50.15365100494701</v>
       </c>
       <c r="D6" t="n">
-        <v>53.59486894596191</v>
+        <v>58.36654460542294</v>
       </c>
       <c r="E6" t="n">
-        <v>61.33714120399702</v>
+        <v>66.57943820589891</v>
       </c>
       <c r="F6" t="n">
-        <v>69.07941346203209</v>
+        <v>74.79233180637482</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>59.55</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>61.08</v>
+        <v>66.11</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>61.59</v>
+        <v>66.64</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.99</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -927,7 +927,7 @@
         <v>37902.77482352941</v>
       </c>
       <c r="D4" t="n">
-        <v>5.305724002472768</v>
+        <v>5.305724002472767</v>
       </c>
       <c r="E4" t="n">
         <v>1.383087560469826</v>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.08710048881471</v>
+        <v>57.73902568638581</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.13338101872037</v>
+        <v>87.56448213279567</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.67247929880576</v>
+        <v>49.4414314710531</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.970759617697794</v>
+        <v>1.970461715342913</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.622586923303446e-24</v>
+        <v>1.623025689964848e-24</v>
       </c>
     </row>
     <row r="16">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1467.244488186022</v>
+        <v>1450.104928403741</v>
       </c>
     </row>
     <row r="5">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2655.247514379743</v>
+        <v>2638.107954597461</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.13338101872037</v>
+        <v>87.56448213279567</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.13338101872037</v>
+        <v>87.56448213279567</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50.98219039100378</v>
+        <v>50.68999148067343</v>
       </c>
       <c r="F11" t="n">
-        <v>40.31269086731736</v>
+        <v>40.0816430395647</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.67247929880576</v>
+        <v>49.4414314710531</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.38186917125462</v>
+        <v>41.10340932931149</v>
       </c>
       <c r="C2" t="n">
-        <v>49.59476277173053</v>
+        <v>49.28149544954451</v>
       </c>
       <c r="D2" t="n">
-        <v>57.80765637220647</v>
+        <v>57.45958156977757</v>
       </c>
       <c r="E2" t="n">
-        <v>66.02054997268243</v>
+        <v>65.6376676900106</v>
       </c>
       <c r="F2" t="n">
-        <v>74.23344357315834</v>
+        <v>73.81575381024366</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.52159122955874</v>
+        <v>41.24313138761561</v>
       </c>
       <c r="C3" t="n">
-        <v>49.73448483003465</v>
+        <v>49.42121750784864</v>
       </c>
       <c r="D3" t="n">
-        <v>57.94737843051058</v>
+        <v>57.59930362808169</v>
       </c>
       <c r="E3" t="n">
-        <v>66.16027203098655</v>
+        <v>65.77738974831472</v>
       </c>
       <c r="F3" t="n">
-        <v>74.37316563146246</v>
+        <v>73.95547586854778</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.66131328786287</v>
+        <v>41.38285344591973</v>
       </c>
       <c r="C4" t="n">
-        <v>49.87420688833877</v>
+        <v>49.56093956615275</v>
       </c>
       <c r="D4" t="n">
-        <v>58.08710048881471</v>
+        <v>57.73902568638581</v>
       </c>
       <c r="E4" t="n">
-        <v>66.29999408929066</v>
+        <v>65.91711180661883</v>
       </c>
       <c r="F4" t="n">
-        <v>74.51288768976659</v>
+        <v>74.09519792685191</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.80103534616698</v>
+        <v>41.52257550422385</v>
       </c>
       <c r="C5" t="n">
-        <v>50.01392894664289</v>
+        <v>49.70066162445688</v>
       </c>
       <c r="D5" t="n">
-        <v>58.22682254711883</v>
+        <v>57.87874774468993</v>
       </c>
       <c r="E5" t="n">
-        <v>66.43971614759479</v>
+        <v>66.05683386492296</v>
       </c>
       <c r="F5" t="n">
-        <v>74.6526097480707</v>
+        <v>74.23491998515603</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.94075740447111</v>
+        <v>41.66229756252797</v>
       </c>
       <c r="C6" t="n">
-        <v>50.15365100494701</v>
+        <v>49.84038368276099</v>
       </c>
       <c r="D6" t="n">
-        <v>58.36654460542294</v>
+        <v>58.01846980299405</v>
       </c>
       <c r="E6" t="n">
-        <v>66.57943820589891</v>
+        <v>66.19655592322707</v>
       </c>
       <c r="F6" t="n">
-        <v>74.79233180637482</v>
+        <v>74.37464204346014</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>64.53</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>66.11</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>66.64</v>
+        <v>66.29000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.11</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.73902568638581</v>
+        <v>60.65898312734051</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.4414314710531</v>
+        <v>59.17462294090208</v>
       </c>
     </row>
     <row r="9">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50.68999148067343</v>
+        <v>62.99925216141439</v>
       </c>
       <c r="F11" t="n">
-        <v>40.0816430395647</v>
+        <v>49.81483450941368</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>49.4414314710531</v>
+        <v>59.17462294090208</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.10340932931149</v>
+        <v>43.66377932829815</v>
       </c>
       <c r="C2" t="n">
-        <v>49.28149544954451</v>
+        <v>51.65366177977295</v>
       </c>
       <c r="D2" t="n">
-        <v>57.45958156977757</v>
+        <v>59.64354423124776</v>
       </c>
       <c r="E2" t="n">
-        <v>65.6376676900106</v>
+        <v>67.63342668272256</v>
       </c>
       <c r="F2" t="n">
-        <v>73.81575381024366</v>
+        <v>75.62330913419738</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.24313138761561</v>
+        <v>44.17149877634452</v>
       </c>
       <c r="C3" t="n">
-        <v>49.42121750784864</v>
+        <v>52.16138122781931</v>
       </c>
       <c r="D3" t="n">
-        <v>57.59930362808169</v>
+        <v>60.15126367929413</v>
       </c>
       <c r="E3" t="n">
-        <v>65.77738974831472</v>
+        <v>68.14114613076893</v>
       </c>
       <c r="F3" t="n">
-        <v>73.95547586854778</v>
+        <v>76.13102858224374</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.38285344591973</v>
+        <v>44.67921822439089</v>
       </c>
       <c r="C4" t="n">
-        <v>49.56093956615275</v>
+        <v>52.66910067586568</v>
       </c>
       <c r="D4" t="n">
-        <v>57.73902568638581</v>
+        <v>60.65898312734051</v>
       </c>
       <c r="E4" t="n">
-        <v>65.91711180661883</v>
+        <v>68.64886557881529</v>
       </c>
       <c r="F4" t="n">
-        <v>74.09519792685191</v>
+        <v>76.63874803029012</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.52257550422385</v>
+        <v>45.18693767243725</v>
       </c>
       <c r="C5" t="n">
-        <v>49.70066162445688</v>
+        <v>53.17682012391205</v>
       </c>
       <c r="D5" t="n">
-        <v>57.87874774468993</v>
+        <v>61.16670257538686</v>
       </c>
       <c r="E5" t="n">
-        <v>66.05683386492296</v>
+        <v>69.15658502686166</v>
       </c>
       <c r="F5" t="n">
-        <v>74.23491998515603</v>
+        <v>77.14646747833649</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.66229756252797</v>
+        <v>45.69465712048363</v>
       </c>
       <c r="C6" t="n">
-        <v>49.84038368276099</v>
+        <v>53.68453957195842</v>
       </c>
       <c r="D6" t="n">
-        <v>58.01846980299405</v>
+        <v>61.67442202343324</v>
       </c>
       <c r="E6" t="n">
-        <v>66.19655592322707</v>
+        <v>69.66430447490804</v>
       </c>
       <c r="F6" t="n">
-        <v>74.37464204346014</v>
+        <v>77.65418692638286</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>64.18000000000001</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>65.76000000000001</v>
+        <v>63.71</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>66.29000000000001</v>
+        <v>63.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.65898312734051</v>
+        <v>60.74498464057621</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.56448213279567</v>
+        <v>87.69652199486377</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.17462294090208</v>
+        <v>59.24562954364323</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.970461715342913</v>
+        <v>1.785605847452086</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.623025689964848e-24</v>
+        <v>1.624497591143552e-24</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>310.3194031417837</v>
+        <v>314.2974476863462</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2638.107954597461</v>
+        <v>2642.085999142023</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.56448213279567</v>
+        <v>87.69652199486377</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.56448213279567</v>
+        <v>87.69652199486377</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>62.99925216141439</v>
+        <v>63.0890519753708</v>
       </c>
       <c r="F11" t="n">
-        <v>49.81483450941368</v>
+        <v>49.88584111215482</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.17462294090208</v>
+        <v>59.24562954364323</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.66377932829815</v>
+        <v>43.73258053888672</v>
       </c>
       <c r="C2" t="n">
-        <v>51.65366177977295</v>
+        <v>51.73106314168508</v>
       </c>
       <c r="D2" t="n">
-        <v>59.64354423124776</v>
+        <v>59.72954574448347</v>
       </c>
       <c r="E2" t="n">
-        <v>67.63342668272256</v>
+        <v>67.72802834728185</v>
       </c>
       <c r="F2" t="n">
-        <v>75.62330913419738</v>
+        <v>75.72651095008024</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.17149877634452</v>
+        <v>44.2402999869331</v>
       </c>
       <c r="C3" t="n">
-        <v>52.16138122781931</v>
+        <v>52.23878258973145</v>
       </c>
       <c r="D3" t="n">
-        <v>60.15126367929413</v>
+        <v>60.23726519252984</v>
       </c>
       <c r="E3" t="n">
-        <v>68.14114613076893</v>
+        <v>68.23574779532822</v>
       </c>
       <c r="F3" t="n">
-        <v>76.13102858224374</v>
+        <v>76.2342303981266</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.67921822439089</v>
+        <v>44.74801943497946</v>
       </c>
       <c r="C4" t="n">
-        <v>52.66910067586568</v>
+        <v>52.74650203777782</v>
       </c>
       <c r="D4" t="n">
-        <v>60.65898312734051</v>
+        <v>60.74498464057621</v>
       </c>
       <c r="E4" t="n">
-        <v>68.64886557881529</v>
+        <v>68.74346724337458</v>
       </c>
       <c r="F4" t="n">
-        <v>76.63874803029012</v>
+        <v>76.74194984617297</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.18693767243725</v>
+        <v>45.25573888302583</v>
       </c>
       <c r="C5" t="n">
-        <v>53.17682012391205</v>
+        <v>53.25422148582419</v>
       </c>
       <c r="D5" t="n">
-        <v>61.16670257538686</v>
+        <v>61.25270408862258</v>
       </c>
       <c r="E5" t="n">
-        <v>69.15658502686166</v>
+        <v>69.25118669142095</v>
       </c>
       <c r="F5" t="n">
-        <v>77.14646747833649</v>
+        <v>77.24966929421933</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.69465712048363</v>
+        <v>45.7634583310722</v>
       </c>
       <c r="C6" t="n">
-        <v>53.68453957195842</v>
+        <v>53.76194093387056</v>
       </c>
       <c r="D6" t="n">
-        <v>61.67442202343324</v>
+        <v>61.76042353666895</v>
       </c>
       <c r="E6" t="n">
-        <v>69.66430447490804</v>
+        <v>69.75890613946733</v>
       </c>
       <c r="F6" t="n">
-        <v>77.65418692638286</v>
+        <v>77.75738874226572</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>63.11</v>
+        <v>63.19</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>63.71</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>63.91</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.29</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.74498464057621</v>
+        <v>60.34390115113507</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.69652199486377</v>
+        <v>86.95377123570114</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.24562954364323</v>
+        <v>59.1218441521384</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.785605847452086</v>
+        <v>1.781743215170423</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.624497591143552e-24</v>
+        <v>1.621644323459585e-24</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1060.061941602162</v>
+        <v>1032.488941602162</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1450.104928403741</v>
+        <v>1447.633228403741</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.07899636618</v>
+        <v>230.0163963661799</v>
       </c>
     </row>
     <row r="6">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.79335175026156</v>
+        <v>107.5233517502616</v>
       </c>
     </row>
     <row r="8">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2642.085999142023</v>
+        <v>2619.708699142024</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.69652199486377</v>
+        <v>86.95377123570114</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.69652199486377</v>
+        <v>86.95377123570114</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63.0890519753708</v>
+        <v>62.93250448966474</v>
       </c>
       <c r="F11" t="n">
-        <v>49.88584111215482</v>
+        <v>49.76205572065</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.24562954364323</v>
+        <v>59.1218441521384</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.73258053888672</v>
+        <v>43.41171374733382</v>
       </c>
       <c r="C2" t="n">
-        <v>51.73106314168508</v>
+        <v>51.37008800118807</v>
       </c>
       <c r="D2" t="n">
-        <v>59.72954574448347</v>
+        <v>59.32846225504233</v>
       </c>
       <c r="E2" t="n">
-        <v>67.72802834728185</v>
+        <v>67.2868365088966</v>
       </c>
       <c r="F2" t="n">
-        <v>75.72651095008024</v>
+        <v>75.24521076275087</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.2402999869331</v>
+        <v>43.91943319538019</v>
       </c>
       <c r="C3" t="n">
-        <v>52.23878258973145</v>
+        <v>51.87780744923443</v>
       </c>
       <c r="D3" t="n">
-        <v>60.23726519252984</v>
+        <v>59.83618170308871</v>
       </c>
       <c r="E3" t="n">
-        <v>68.23574779532822</v>
+        <v>67.79455595694297</v>
       </c>
       <c r="F3" t="n">
-        <v>76.2342303981266</v>
+        <v>75.75293021079725</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.74801943497946</v>
+        <v>44.42715264342656</v>
       </c>
       <c r="C4" t="n">
-        <v>52.74650203777782</v>
+        <v>52.3855268972808</v>
       </c>
       <c r="D4" t="n">
-        <v>60.74498464057621</v>
+        <v>60.34390115113507</v>
       </c>
       <c r="E4" t="n">
-        <v>68.74346724337458</v>
+        <v>68.30227540498935</v>
       </c>
       <c r="F4" t="n">
-        <v>76.74194984617297</v>
+        <v>76.26064965884362</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.25573888302583</v>
+        <v>44.93487209147293</v>
       </c>
       <c r="C5" t="n">
-        <v>53.25422148582419</v>
+        <v>52.89324634532717</v>
       </c>
       <c r="D5" t="n">
-        <v>61.25270408862258</v>
+        <v>60.85162059918144</v>
       </c>
       <c r="E5" t="n">
-        <v>69.25118669142095</v>
+        <v>68.8099948530357</v>
       </c>
       <c r="F5" t="n">
-        <v>77.24966929421933</v>
+        <v>76.76836910688999</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.7634583310722</v>
+        <v>45.4425915395193</v>
       </c>
       <c r="C6" t="n">
-        <v>53.76194093387056</v>
+        <v>53.40096579337354</v>
       </c>
       <c r="D6" t="n">
-        <v>61.76042353666895</v>
+        <v>61.35934004722782</v>
       </c>
       <c r="E6" t="n">
-        <v>69.75890613946733</v>
+        <v>69.31771430108208</v>
       </c>
       <c r="F6" t="n">
-        <v>77.75738874226572</v>
+        <v>77.27608855493636</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>63.19</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>63.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.72</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.34390115113507</v>
+        <v>61.29119122740811</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86.95377123570114</v>
+        <v>88.69642895725968</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.1218441521384</v>
+        <v>59.43313679450291</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.781743215170423</v>
+        <v>1.785936763211487</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.621644323459585e-24</v>
+        <v>1.621926814911631e-24</v>
       </c>
     </row>
     <row r="16">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1032.488941602162</v>
+        <v>1073.424241602162</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1447.633228403741</v>
+        <v>1455.722428403741</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230.0163963661799</v>
+        <v>233.4939963661799</v>
       </c>
     </row>
     <row r="6">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2619.708699142024</v>
+        <v>2672.210799142023</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86.95377123570114</v>
+        <v>88.69642895725968</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86.95377123570114</v>
+        <v>88.69642895725968</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>62.93250448966474</v>
+        <v>63.32618648952381</v>
       </c>
       <c r="F11" t="n">
-        <v>49.76205572065</v>
+        <v>50.0733483630145</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.1218441521384</v>
+        <v>59.43313679450291</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.41171374733382</v>
+        <v>44.16954580835225</v>
       </c>
       <c r="C2" t="n">
-        <v>51.37008800118807</v>
+        <v>52.2226490698338</v>
       </c>
       <c r="D2" t="n">
-        <v>59.32846225504233</v>
+        <v>60.27575233131537</v>
       </c>
       <c r="E2" t="n">
-        <v>67.2868365088966</v>
+        <v>68.32885559279694</v>
       </c>
       <c r="F2" t="n">
-        <v>75.24521076275087</v>
+        <v>76.38195885427851</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.91943319538019</v>
+        <v>44.67726525639862</v>
       </c>
       <c r="C3" t="n">
-        <v>51.87780744923443</v>
+        <v>52.73036851788017</v>
       </c>
       <c r="D3" t="n">
-        <v>59.83618170308871</v>
+        <v>60.78347177936174</v>
       </c>
       <c r="E3" t="n">
-        <v>67.79455595694297</v>
+        <v>68.83657504084331</v>
       </c>
       <c r="F3" t="n">
-        <v>75.75293021079725</v>
+        <v>76.88967830232488</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.42715264342656</v>
+        <v>45.18498470444499</v>
       </c>
       <c r="C4" t="n">
-        <v>52.3855268972808</v>
+        <v>53.23808796592654</v>
       </c>
       <c r="D4" t="n">
-        <v>60.34390115113507</v>
+        <v>61.29119122740811</v>
       </c>
       <c r="E4" t="n">
-        <v>68.30227540498935</v>
+        <v>69.34429448888967</v>
       </c>
       <c r="F4" t="n">
-        <v>76.26064965884362</v>
+        <v>77.39739775037125</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.93487209147293</v>
+        <v>45.69270415249136</v>
       </c>
       <c r="C5" t="n">
-        <v>52.89324634532717</v>
+        <v>53.7458074139729</v>
       </c>
       <c r="D5" t="n">
-        <v>60.85162059918144</v>
+        <v>61.79891067545448</v>
       </c>
       <c r="E5" t="n">
-        <v>68.8099948530357</v>
+        <v>69.85201393693605</v>
       </c>
       <c r="F5" t="n">
-        <v>76.76836910688999</v>
+        <v>77.90511719841763</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.4425915395193</v>
+        <v>46.20042360053773</v>
       </c>
       <c r="C6" t="n">
-        <v>53.40096579337354</v>
+        <v>54.25352686201927</v>
       </c>
       <c r="D6" t="n">
-        <v>61.35934004722782</v>
+        <v>62.30663012350085</v>
       </c>
       <c r="E6" t="n">
-        <v>69.31771430108208</v>
+        <v>70.35973338498242</v>
       </c>
       <c r="F6" t="n">
-        <v>77.27608855493636</v>
+        <v>78.412836646464</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>62.79</v>
+        <v>63.74</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>63.4</v>
+        <v>64.34</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>63.6</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.621926814911631e-24</v>
+        <v>1.62192681491163e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.62192681491163e-24</v>
+        <v>1.621926814911631e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.76</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.62192681491163e-24</v>
+        <v>1.621926814911631e-24</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.62192681491163e-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -1334,7 +1334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.37</v>
+        <v>37.37</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.37</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.22</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.66</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.83</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.29119122740811</v>
+        <v>61.32790254920243</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.69642895725968</v>
+        <v>88.76082173354527</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.43313679450291</v>
+        <v>59.45033299921749</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.785936763211487</v>
+        <v>1.785732723256765</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107.5233517502616</v>
+        <v>109.4633517502616</v>
       </c>
     </row>
     <row r="8">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2672.210799142023</v>
+        <v>2674.150799142024</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.69642895725968</v>
+        <v>88.76082173354527</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.69642895725968</v>
+        <v>88.76082173354527</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63.32618648952381</v>
+        <v>63.34793398798892</v>
       </c>
       <c r="F11" t="n">
-        <v>50.0733483630145</v>
+        <v>50.09054456772908</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.43313679450291</v>
+        <v>59.45033299921749</v>
       </c>
     </row>
     <row r="13">
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.16954580835225</v>
+        <v>44.1989148657877</v>
       </c>
       <c r="C2" t="n">
-        <v>52.2226490698338</v>
+        <v>52.25568925944867</v>
       </c>
       <c r="D2" t="n">
-        <v>60.27575233131537</v>
+        <v>60.31246365310969</v>
       </c>
       <c r="E2" t="n">
-        <v>68.32885559279694</v>
+        <v>68.36923804677068</v>
       </c>
       <c r="F2" t="n">
-        <v>76.38195885427851</v>
+        <v>76.42601244043169</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.67726525639862</v>
+        <v>44.70663431383407</v>
       </c>
       <c r="C3" t="n">
-        <v>52.73036851788017</v>
+        <v>52.76340870749505</v>
       </c>
       <c r="D3" t="n">
-        <v>60.78347177936174</v>
+        <v>60.82018310115605</v>
       </c>
       <c r="E3" t="n">
-        <v>68.83657504084331</v>
+        <v>68.87695749481705</v>
       </c>
       <c r="F3" t="n">
-        <v>76.88967830232488</v>
+        <v>76.93373188847806</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.18498470444499</v>
+        <v>45.21435376188044</v>
       </c>
       <c r="C4" t="n">
-        <v>53.23808796592654</v>
+        <v>53.27112815554142</v>
       </c>
       <c r="D4" t="n">
-        <v>61.29119122740811</v>
+        <v>61.32790254920243</v>
       </c>
       <c r="E4" t="n">
-        <v>69.34429448888967</v>
+        <v>69.38467694286342</v>
       </c>
       <c r="F4" t="n">
-        <v>77.39739775037125</v>
+        <v>77.44145133652444</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.69270415249136</v>
+        <v>45.7220732099268</v>
       </c>
       <c r="C5" t="n">
-        <v>53.7458074139729</v>
+        <v>53.77884760358778</v>
       </c>
       <c r="D5" t="n">
-        <v>61.79891067545448</v>
+        <v>61.83562199724879</v>
       </c>
       <c r="E5" t="n">
-        <v>69.85201393693605</v>
+        <v>69.89239639090979</v>
       </c>
       <c r="F5" t="n">
-        <v>77.90511719841763</v>
+        <v>77.9491707845708</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.20042360053773</v>
+        <v>46.22979265797317</v>
       </c>
       <c r="C6" t="n">
-        <v>54.25352686201927</v>
+        <v>54.28656705163415</v>
       </c>
       <c r="D6" t="n">
-        <v>62.30663012350085</v>
+        <v>62.34334144529517</v>
       </c>
       <c r="E6" t="n">
-        <v>70.35973338498242</v>
+        <v>70.40011583895615</v>
       </c>
       <c r="F6" t="n">
-        <v>78.412836646464</v>
+        <v>78.45689023261717</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>63.74</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>64.34</v>
+        <v>64.38</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>64.54000000000001</v>
+        <v>64.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.32790254920243</v>
+        <v>59.65801123828565</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88.76082173354527</v>
+        <v>87.34516651357181</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.45033299921749</v>
+        <v>56.1962654887849</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.785732723256765</v>
+        <v>1.753349748109913</v>
       </c>
     </row>
     <row r="12">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>314.2974476863462</v>
+        <v>216.7404965933337</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1073.424241602162</v>
+        <v>1002.930834468437</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1455.722428403741</v>
+        <v>1425.59148817824</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>174.654</v>
       </c>
     </row>
     <row r="12">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2148.2</v>
+        <v>-2136.109</v>
       </c>
     </row>
     <row r="13">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>400</v>
+        <v>442.74</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2674.150799142024</v>
+        <v>2631.500500689785</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.76082173354527</v>
+        <v>87.34516651357181</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.76082173354527</v>
+        <v>87.34516651357181</v>
       </c>
     </row>
     <row r="20">
@@ -833,7 +833,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -880,16 +880,16 @@
         <v>75000</v>
       </c>
       <c r="C2" t="n">
-        <v>36628.77482352941</v>
+        <v>34799.33988235294</v>
       </c>
       <c r="D2" t="n">
-        <v>5.04151191264936</v>
+        <v>4.336428472000167</v>
       </c>
       <c r="E2" t="n">
-        <v>1.332887263403379</v>
+        <v>1.198921409680032</v>
       </c>
       <c r="F2" t="n">
-        <v>1.298561950416303</v>
+        <v>1.168046065782534</v>
       </c>
     </row>
     <row r="3">
@@ -902,16 +902,16 @@
         <v>88000</v>
       </c>
       <c r="C3" t="n">
-        <v>38994.77482352941</v>
+        <v>36658.33988235294</v>
       </c>
       <c r="D3" t="n">
-        <v>5.501661365959667</v>
+        <v>4.758056518546054</v>
       </c>
       <c r="E3" t="n">
-        <v>1.420315659532337</v>
+        <v>1.27903073852375</v>
       </c>
       <c r="F3" t="n">
-        <v>1.348103964737602</v>
+        <v>1.214002252283041</v>
       </c>
     </row>
     <row r="4">
@@ -924,16 +924,16 @@
         <v>82000</v>
       </c>
       <c r="C4" t="n">
-        <v>37902.77482352941</v>
+        <v>35800.33988235294</v>
       </c>
       <c r="D4" t="n">
-        <v>5.305724002472767</v>
+        <v>4.579904658937441</v>
       </c>
       <c r="E4" t="n">
-        <v>1.383087560469826</v>
+        <v>1.245181885198114</v>
       </c>
       <c r="F4" t="n">
-        <v>1.278961411322773</v>
+        <v>1.151438004912397</v>
       </c>
     </row>
     <row r="5">
@@ -946,16 +946,16 @@
         <v>64000</v>
       </c>
       <c r="C5" t="n">
-        <v>34626.77482352941</v>
+        <v>33226.33988235294</v>
       </c>
       <c r="D5" t="n">
-        <v>4.679325204665986</v>
+        <v>4.00684159530772</v>
       </c>
       <c r="E5" t="n">
-        <v>1.264071788886537</v>
+        <v>1.136299903108467</v>
       </c>
       <c r="F5" t="n">
-        <v>1.138803413411295</v>
+        <v>1.023693606404024</v>
       </c>
     </row>
     <row r="6">
@@ -968,16 +968,16 @@
         <v>59000</v>
       </c>
       <c r="C6" t="n">
-        <v>33716.77482352941</v>
+        <v>32511.33988235294</v>
       </c>
       <c r="D6" t="n">
-        <v>4.510107651912121</v>
+        <v>3.852435401758236</v>
       </c>
       <c r="E6" t="n">
-        <v>1.231920453863303</v>
+        <v>1.106962726334065</v>
       </c>
       <c r="F6" t="n">
-        <v>1.081257025918461</v>
+        <v>0.9715815834740367</v>
       </c>
     </row>
     <row r="7">
@@ -990,16 +990,16 @@
         <v>70000</v>
       </c>
       <c r="C7" t="n">
-        <v>35718.77482352941</v>
+        <v>34084.33988235294</v>
       </c>
       <c r="D7" t="n">
-        <v>4.907912858984188</v>
+        <v>4.217664523205436</v>
       </c>
       <c r="E7" t="n">
-        <v>1.307503443206996</v>
+        <v>1.176356259409033</v>
       </c>
       <c r="F7" t="n">
-        <v>1.118042655489949</v>
+        <v>1.005899053578004</v>
       </c>
     </row>
     <row r="8">
@@ -1012,16 +1012,16 @@
         <v>74000</v>
       </c>
       <c r="C8" t="n">
-        <v>36446.77482352941</v>
+        <v>34656.33988235294</v>
       </c>
       <c r="D8" t="n">
-        <v>5.041505976232845</v>
+        <v>4.339393712049301</v>
       </c>
       <c r="E8" t="n">
-        <v>1.332886135484241</v>
+        <v>1.199484805289367</v>
       </c>
       <c r="F8" t="n">
-        <v>1.110395869562321</v>
+        <v>0.9992623810376681</v>
       </c>
     </row>
     <row r="9">
@@ -1034,16 +1034,16 @@
         <v>56000</v>
       </c>
       <c r="C9" t="n">
-        <v>33170.77482352941</v>
+        <v>32082.33988235294</v>
       </c>
       <c r="D9" t="n">
-        <v>4.418075386683454</v>
+        <v>3.769295888468712</v>
       </c>
       <c r="E9" t="n">
-        <v>1.214434323469856</v>
+        <v>1.091166218809055</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9856621406297021</v>
+        <v>0.8856149815835201</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.359788431488404</v>
+        <v>8.419537929055226</v>
       </c>
     </row>
     <row r="11">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>63.34793398798892</v>
+        <v>60.42172249741822</v>
       </c>
       <c r="F11" t="n">
-        <v>50.09054456772908</v>
+        <v>47.77672755972967</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>59.45033299921749</v>
+        <v>56.1962654887849</v>
       </c>
     </row>
     <row r="13">
@@ -1104,9 +1104,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.1989148657877</v>
+        <v>43.42850855385406</v>
       </c>
       <c r="C2" t="n">
-        <v>52.25568925944867</v>
+        <v>51.08241274879656</v>
       </c>
       <c r="D2" t="n">
-        <v>60.31246365310969</v>
+        <v>58.73631694373908</v>
       </c>
       <c r="E2" t="n">
-        <v>68.36923804677068</v>
+        <v>66.3902211386816</v>
       </c>
       <c r="F2" t="n">
-        <v>76.42601244043169</v>
+        <v>74.04412533362412</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.70663431383407</v>
+        <v>43.88935570112734</v>
       </c>
       <c r="C3" t="n">
-        <v>52.76340870749505</v>
+        <v>51.54325989606984</v>
       </c>
       <c r="D3" t="n">
-        <v>60.82018310115605</v>
+        <v>59.19716409101236</v>
       </c>
       <c r="E3" t="n">
-        <v>68.87695749481705</v>
+        <v>66.85106828595488</v>
       </c>
       <c r="F3" t="n">
-        <v>76.93373188847806</v>
+        <v>74.50497248089741</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.21435376188044</v>
+        <v>44.35020284840063</v>
       </c>
       <c r="C4" t="n">
-        <v>53.27112815554142</v>
+        <v>52.00410704334313</v>
       </c>
       <c r="D4" t="n">
-        <v>61.32790254920243</v>
+        <v>59.65801123828565</v>
       </c>
       <c r="E4" t="n">
-        <v>69.38467694286342</v>
+        <v>67.31191543322817</v>
       </c>
       <c r="F4" t="n">
-        <v>77.44145133652444</v>
+        <v>74.96581962817069</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.7220732099268</v>
+        <v>44.81104999567392</v>
       </c>
       <c r="C5" t="n">
-        <v>53.77884760358778</v>
+        <v>52.46495419061642</v>
       </c>
       <c r="D5" t="n">
-        <v>61.83562199724879</v>
+        <v>60.11885838555894</v>
       </c>
       <c r="E5" t="n">
-        <v>69.89239639090979</v>
+        <v>67.77276258050145</v>
       </c>
       <c r="F5" t="n">
-        <v>77.9491707845708</v>
+        <v>75.42666677544399</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.22979265797317</v>
+        <v>45.2718971429472</v>
       </c>
       <c r="C6" t="n">
-        <v>54.28656705163415</v>
+        <v>52.92580133788971</v>
       </c>
       <c r="D6" t="n">
-        <v>62.34334144529517</v>
+        <v>60.57970553283222</v>
       </c>
       <c r="E6" t="n">
-        <v>70.40011583895615</v>
+        <v>68.23360972777475</v>
       </c>
       <c r="F6" t="n">
-        <v>78.45689023261717</v>
+        <v>75.88751392271728</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>63.78</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>64.38</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>64.58</v>
+        <v>62.45</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.75</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.65801123828565</v>
+        <v>59.78169459542286</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.34516651357181</v>
+        <v>87.56743823636469</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.1962654887849</v>
+        <v>56.24549953201392</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.753349748109913</v>
+        <v>1.753764585739854</v>
       </c>
     </row>
     <row r="12">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>216.7404965933337</v>
+        <v>213.5137713642919</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1002.930834468437</v>
+        <v>1015.027243962967</v>
       </c>
     </row>
     <row r="4">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233.4939963661799</v>
+        <v>231.326975629037</v>
       </c>
     </row>
     <row r="6">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109.4633517502616</v>
+        <v>109.457202444347</v>
       </c>
     </row>
     <row r="8">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2631.500500689785</v>
+        <v>2638.197014912216</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.34516651357181</v>
+        <v>87.56743823636469</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.34516651357181</v>
+        <v>87.56743823636469</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>60.42172249741822</v>
+        <v>60.4839872411408</v>
       </c>
       <c r="F11" t="n">
-        <v>47.77672755972967</v>
+        <v>47.8259616029587</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.1962654887849</v>
+        <v>56.24549953201392</v>
       </c>
     </row>
     <row r="13">
@@ -1104,9 +1104,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.42850855385406</v>
+        <v>43.52745523956384</v>
       </c>
       <c r="C2" t="n">
-        <v>51.08241274879656</v>
+        <v>51.19372777022006</v>
       </c>
       <c r="D2" t="n">
-        <v>58.73631694373908</v>
+        <v>58.86000030087629</v>
       </c>
       <c r="E2" t="n">
-        <v>66.3902211386816</v>
+        <v>66.52627283153257</v>
       </c>
       <c r="F2" t="n">
-        <v>74.04412533362412</v>
+        <v>74.19254536218881</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.88935570112734</v>
+        <v>43.98830238683713</v>
       </c>
       <c r="C3" t="n">
-        <v>51.54325989606984</v>
+        <v>51.65457491749335</v>
       </c>
       <c r="D3" t="n">
-        <v>59.19716409101236</v>
+        <v>59.32084744814958</v>
       </c>
       <c r="E3" t="n">
-        <v>66.85106828595488</v>
+        <v>66.98711997880585</v>
       </c>
       <c r="F3" t="n">
-        <v>74.50497248089741</v>
+        <v>74.65339250946209</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.35020284840063</v>
+        <v>44.44914953411042</v>
       </c>
       <c r="C4" t="n">
-        <v>52.00410704334313</v>
+        <v>52.11542206476664</v>
       </c>
       <c r="D4" t="n">
-        <v>59.65801123828565</v>
+        <v>59.78169459542286</v>
       </c>
       <c r="E4" t="n">
-        <v>67.31191543322817</v>
+        <v>67.44796712607913</v>
       </c>
       <c r="F4" t="n">
-        <v>74.96581962817069</v>
+        <v>75.11423965673538</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.81104999567392</v>
+        <v>44.9099966813837</v>
       </c>
       <c r="C5" t="n">
-        <v>52.46495419061642</v>
+        <v>52.57626921203993</v>
       </c>
       <c r="D5" t="n">
-        <v>60.11885838555894</v>
+        <v>60.24254174269615</v>
       </c>
       <c r="E5" t="n">
-        <v>67.77276258050145</v>
+        <v>67.90881427335242</v>
       </c>
       <c r="F5" t="n">
-        <v>75.42666677544399</v>
+        <v>75.57508680400868</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.2718971429472</v>
+        <v>45.37084382865699</v>
       </c>
       <c r="C6" t="n">
-        <v>52.92580133788971</v>
+        <v>53.03711635931322</v>
       </c>
       <c r="D6" t="n">
-        <v>60.57970553283222</v>
+        <v>60.70338888996945</v>
       </c>
       <c r="E6" t="n">
-        <v>68.23360972777475</v>
+        <v>68.36966142062572</v>
       </c>
       <c r="F6" t="n">
-        <v>75.88751392271728</v>
+        <v>76.03593395128196</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>61.76</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>62.28</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>62.45</v>
+        <v>62.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.62</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.86</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.4</v>
+        <v>40.23</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.23</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.78169459542286</v>
+        <v>60.15377774688849</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87.56743823636469</v>
+        <v>88.15561863961638</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.24549953201392</v>
+        <v>56.52508204492155</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.753764585739854</v>
+        <v>1.759128885977417</v>
       </c>
     </row>
     <row r="12">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213.5137713642919</v>
+        <v>233.5142858206506</v>
       </c>
     </row>
     <row r="3">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.326975629037</v>
+        <v>229.0469268542248</v>
       </c>
     </row>
     <row r="6">
@@ -773,7 +773,7 @@
         <v/>
       </c>
       <c r="B16" t="n">
-        <v>2638.197014912216</v>
+        <v>2655.917480593762</v>
       </c>
     </row>
     <row r="17">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.56743823636469</v>
+        <v>88.15561863961638</v>
       </c>
     </row>
     <row r="19">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.56743823636469</v>
+        <v>88.15561863961638</v>
       </c>
     </row>
     <row r="20">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>60.4839872411408</v>
+        <v>60.8375664390655</v>
       </c>
       <c r="F11" t="n">
-        <v>47.8259616029587</v>
+        <v>48.10554411586633</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.24549953201392</v>
+        <v>56.52508204492155</v>
       </c>
     </row>
     <row r="13">
@@ -1105,8 +1105,8 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.52745523956384</v>
+        <v>43.82512176073634</v>
       </c>
       <c r="C2" t="n">
-        <v>51.19372777022006</v>
+        <v>51.52860260653912</v>
       </c>
       <c r="D2" t="n">
-        <v>58.86000030087629</v>
+        <v>59.23208345234191</v>
       </c>
       <c r="E2" t="n">
-        <v>66.52627283153257</v>
+        <v>66.93556429814474</v>
       </c>
       <c r="F2" t="n">
-        <v>74.19254536218881</v>
+        <v>74.63904514394756</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.98830238683713</v>
+        <v>44.28596890800962</v>
       </c>
       <c r="C3" t="n">
-        <v>51.65457491749335</v>
+        <v>51.9894497538124</v>
       </c>
       <c r="D3" t="n">
-        <v>59.32084744814958</v>
+        <v>59.6929305996152</v>
       </c>
       <c r="E3" t="n">
-        <v>66.98711997880585</v>
+        <v>67.39641144541802</v>
       </c>
       <c r="F3" t="n">
-        <v>74.65339250946209</v>
+        <v>75.09989229122085</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.44914953411042</v>
+        <v>44.74681605528291</v>
       </c>
       <c r="C4" t="n">
-        <v>52.11542206476664</v>
+        <v>52.45029690108569</v>
       </c>
       <c r="D4" t="n">
-        <v>59.78169459542286</v>
+        <v>60.15377774688849</v>
       </c>
       <c r="E4" t="n">
-        <v>67.44796712607913</v>
+        <v>67.85725859269131</v>
       </c>
       <c r="F4" t="n">
-        <v>75.11423965673538</v>
+        <v>75.56073943849414</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.9099966813837</v>
+        <v>45.2076632025562</v>
       </c>
       <c r="C5" t="n">
-        <v>52.57626921203993</v>
+        <v>52.91114404835898</v>
       </c>
       <c r="D5" t="n">
-        <v>60.24254174269615</v>
+        <v>60.61462489416178</v>
       </c>
       <c r="E5" t="n">
-        <v>67.90881427335242</v>
+        <v>68.31810573996461</v>
       </c>
       <c r="F5" t="n">
-        <v>75.57508680400868</v>
+        <v>76.02158658576742</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.37084382865699</v>
+        <v>45.66851034982949</v>
       </c>
       <c r="C6" t="n">
-        <v>53.03711635931322</v>
+        <v>53.37199119563226</v>
       </c>
       <c r="D6" t="n">
-        <v>60.70338888996945</v>
+        <v>61.07547204143506</v>
       </c>
       <c r="E6" t="n">
-        <v>68.36966142062572</v>
+        <v>68.77895288723789</v>
       </c>
       <c r="F6" t="n">
-        <v>76.03593395128196</v>
+        <v>76.48243373304071</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>61.89</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>62.41</v>
+        <v>62.78</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>62.58</v>
+        <v>62.95</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.15377774688849</v>
+        <v>59.21138461510683</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56.52508204492155</v>
+        <v>53.38377160564936</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56250</v>
+        <v>51450</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77250</v>
+        <v>55675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.759128885977417</v>
+        <v>1.65884157058753</v>
       </c>
     </row>
     <row r="12">
@@ -877,19 +877,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75000</v>
+        <v>59900</v>
       </c>
       <c r="C2" t="n">
-        <v>34799.33988235294</v>
+        <v>32640.03988235294</v>
       </c>
       <c r="D2" t="n">
-        <v>4.336428472000167</v>
+        <v>4.237764339062011</v>
       </c>
       <c r="E2" t="n">
-        <v>1.198921409680032</v>
+        <v>1.180175224421782</v>
       </c>
       <c r="F2" t="n">
-        <v>1.168046065782534</v>
+        <v>1.149782643541061</v>
       </c>
     </row>
     <row r="3">
@@ -899,19 +899,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88000</v>
+        <v>59900</v>
       </c>
       <c r="C3" t="n">
-        <v>36658.33988235294</v>
+        <v>32640.03988235294</v>
       </c>
       <c r="D3" t="n">
-        <v>4.758056518546054</v>
+        <v>4.237764339062011</v>
       </c>
       <c r="E3" t="n">
-        <v>1.27903073852375</v>
+        <v>1.180175224421782</v>
       </c>
       <c r="F3" t="n">
-        <v>1.214002252283041</v>
+        <v>1.120172750648934</v>
       </c>
     </row>
     <row r="4">
@@ -921,19 +921,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82000</v>
+        <v>51450</v>
       </c>
       <c r="C4" t="n">
-        <v>35800.33988235294</v>
+        <v>31431.68988235294</v>
       </c>
       <c r="D4" t="n">
-        <v>4.579904658937441</v>
+        <v>3.700280742582396</v>
       </c>
       <c r="E4" t="n">
-        <v>1.245181885198114</v>
+        <v>1.078053341090655</v>
       </c>
       <c r="F4" t="n">
-        <v>1.151438004912397</v>
+        <v>0.9968917818436381</v>
       </c>
     </row>
     <row r="5">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64000</v>
+        <v>51450</v>
       </c>
       <c r="C5" t="n">
-        <v>33226.33988235294</v>
+        <v>31431.68988235294</v>
       </c>
       <c r="D5" t="n">
-        <v>4.00684159530772</v>
+        <v>3.700280742582396</v>
       </c>
       <c r="E5" t="n">
-        <v>1.136299903108467</v>
+        <v>1.078053341090655</v>
       </c>
       <c r="F5" t="n">
-        <v>1.023693606404024</v>
+        <v>0.9712192262077975</v>
       </c>
     </row>
     <row r="6">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59000</v>
+        <v>38000</v>
       </c>
       <c r="C6" t="n">
-        <v>32511.33988235294</v>
+        <v>29508.33988235294</v>
       </c>
       <c r="D6" t="n">
-        <v>3.852435401758236</v>
+        <v>3.218167587040284</v>
       </c>
       <c r="E6" t="n">
-        <v>1.106962726334065</v>
+        <v>0.986451841537654</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9715815834740367</v>
+        <v>0.8658091364973358</v>
       </c>
     </row>
     <row r="7">
@@ -987,19 +987,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70000</v>
+        <v>38000</v>
       </c>
       <c r="C7" t="n">
-        <v>34084.33988235294</v>
+        <v>29508.33988235294</v>
       </c>
       <c r="D7" t="n">
-        <v>4.217664523205436</v>
+        <v>3.218167587040284</v>
       </c>
       <c r="E7" t="n">
-        <v>1.176356259409033</v>
+        <v>0.986451841537654</v>
       </c>
       <c r="F7" t="n">
-        <v>1.005899053578004</v>
+        <v>0.8435122998380551</v>
       </c>
     </row>
     <row r="8">
@@ -1009,19 +1009,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74000</v>
+        <v>38000</v>
       </c>
       <c r="C8" t="n">
-        <v>34656.33988235294</v>
+        <v>29508.33988235294</v>
       </c>
       <c r="D8" t="n">
-        <v>4.339393712049301</v>
+        <v>3.218167587040284</v>
       </c>
       <c r="E8" t="n">
-        <v>1.199484805289367</v>
+        <v>0.986451841537654</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9992623810376681</v>
+        <v>0.8217896647020131</v>
       </c>
     </row>
     <row r="9">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56000</v>
+        <v>38000</v>
       </c>
       <c r="C9" t="n">
-        <v>32082.33988235294</v>
+        <v>29508.33988235294</v>
       </c>
       <c r="D9" t="n">
-        <v>3.769295888468712</v>
+        <v>3.218167587040284</v>
       </c>
       <c r="E9" t="n">
-        <v>1.091166218809055</v>
+        <v>0.986451841537654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8856149815835201</v>
+        <v>0.8006264439068694</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.419537929055226</v>
+        <v>7.569803947185705</v>
       </c>
     </row>
     <row r="11">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>60.8375664390655</v>
+        <v>57.9394818723128</v>
       </c>
       <c r="F11" t="n">
-        <v>48.10554411586633</v>
+        <v>45.81396765846366</v>
       </c>
     </row>
     <row r="12">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56.52508204492155</v>
+        <v>53.38377160564936</v>
       </c>
     </row>
     <row r="13">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77250</v>
+        <v>55675</v>
       </c>
     </row>
   </sheetData>
@@ -1106,7 +1106,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1150,19 +1150,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.82512176073634</v>
+        <v>43.16544656848917</v>
       </c>
       <c r="C2" t="n">
-        <v>51.52860260653912</v>
+        <v>50.86892741429195</v>
       </c>
       <c r="D2" t="n">
-        <v>59.23208345234191</v>
+        <v>58.57240826009475</v>
       </c>
       <c r="E2" t="n">
-        <v>66.93556429814474</v>
+        <v>66.27588910589758</v>
       </c>
       <c r="F2" t="n">
-        <v>74.63904514394756</v>
+        <v>73.97936995170039</v>
       </c>
     </row>
     <row r="3">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.28596890800962</v>
+        <v>43.48493474599521</v>
       </c>
       <c r="C3" t="n">
-        <v>51.9894497538124</v>
+        <v>51.18841559179799</v>
       </c>
       <c r="D3" t="n">
-        <v>59.6929305996152</v>
+        <v>58.89189643760079</v>
       </c>
       <c r="E3" t="n">
-        <v>67.39641144541802</v>
+        <v>66.59537728340362</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09989229122085</v>
+        <v>74.29885812920644</v>
       </c>
     </row>
     <row r="4">
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.74681605528291</v>
+        <v>43.80442292350125</v>
       </c>
       <c r="C4" t="n">
-        <v>52.45029690108569</v>
+        <v>51.50790376930403</v>
       </c>
       <c r="D4" t="n">
-        <v>60.15377774688849</v>
+        <v>59.21138461510683</v>
       </c>
       <c r="E4" t="n">
-        <v>67.85725859269131</v>
+        <v>66.91486546090965</v>
       </c>
       <c r="F4" t="n">
-        <v>75.56073943849414</v>
+        <v>74.61834630671248</v>
       </c>
     </row>
     <row r="5">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>45.2076632025562</v>
+        <v>44.12391110100729</v>
       </c>
       <c r="C5" t="n">
-        <v>52.91114404835898</v>
+        <v>51.82739194681007</v>
       </c>
       <c r="D5" t="n">
-        <v>60.61462489416178</v>
+        <v>59.53087279261287</v>
       </c>
       <c r="E5" t="n">
-        <v>68.31810573996461</v>
+        <v>67.23435363841568</v>
       </c>
       <c r="F5" t="n">
-        <v>76.02158658576742</v>
+        <v>74.93783448421851</v>
       </c>
     </row>
     <row r="6">
@@ -1238,19 +1238,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.66851034982949</v>
+        <v>44.44339927851333</v>
       </c>
       <c r="C6" t="n">
-        <v>53.37199119563226</v>
+        <v>52.14688012431611</v>
       </c>
       <c r="D6" t="n">
-        <v>61.07547204143506</v>
+        <v>59.85036097011891</v>
       </c>
       <c r="E6" t="n">
-        <v>68.77895288723789</v>
+        <v>67.55384181592173</v>
       </c>
       <c r="F6" t="n">
-        <v>76.48243373304071</v>
+        <v>75.25732266172456</v>
       </c>
     </row>
   </sheetData>
@@ -1288,7 +1288,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>62.26</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="3">
@@ -1296,7 +1296,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>62.78</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="4">
@@ -1304,7 +1304,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>62.95</v>
+        <v>61.61</v>
       </c>
     </row>
   </sheetData>
@@ -1334,7 +1334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.14</v>
+        <v>39.31</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.31</v>
+        <v>41.45</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.45</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ten_fv_report.xlsx
+++ b/outputs/ten_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.27</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="5">
